--- a/astro-site/public/dl/pack-appcc/BONUS-01-registro-formacion.xlsx
+++ b/astro-site/public/dl/pack-appcc/BONUS-01-registro-formacion.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView activeTab="0" autoFilterDateGrouping="1" firstSheet="0" minimized="0" showHorizontalScroll="1" showSheetTabs="1" showVerticalScroll="1" tabRatio="600" visibility="visible"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Formación Personal" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Formación Personal" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="1">
-    <numFmt formatCode="DD/MM/YYYY" numFmtId="164"/>
+    <numFmt numFmtId="164" formatCode="DD/MM/YYYY"/>
   </numFmts>
   <fonts count="8">
     <font>
@@ -111,32 +111,32 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="10">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="2" fontId="5" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="3" fontId="6" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="3" fontId="6" numFmtId="164" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="3" fontId="6" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle builtinId="0" hidden="0" name="Normal" xfId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium9"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -496,15 +496,16 @@
   <sheetPr>
     <tabColor rgb="00FFD700"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:B10"/>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="3"/>
-    <col customWidth="1" max="2" min="2" width="80"/>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="80" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -512,6 +513,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="B4" s="2" t="inlineStr">
         <is>
@@ -519,9 +521,7 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="B5" t="inlineStr"/>
-    </row>
+    <row r="5"/>
     <row r="6">
       <c r="B6" s="3" t="inlineStr">
         <is>
@@ -543,13 +543,19 @@
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="B9" t="inlineStr"/>
-    </row>
+    <row r="9"/>
     <row r="10">
       <c r="B10" s="2" t="inlineStr">
         <is>
           <t>— Pack de Plantillas APPCC · AI Chef Pro · aichef.pro</t>
+        </is>
+      </c>
+    </row>
+    <row r="11"/>
+    <row r="12">
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Versión 1.1 · agosto 2026 · aichef.pro/pack-appcc · info@aichef.pro</t>
         </is>
       </c>
     </row>
@@ -557,7 +563,16 @@
   <mergeCells count="1">
     <mergeCell ref="B2"/>
   </mergeCells>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -566,19 +581,19 @@
   <sheetPr>
     <tabColor rgb="00FFD700"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:H26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="22"/>
-    <col customWidth="1" max="2" min="2" width="15"/>
-    <col customWidth="1" max="3" min="3" width="30"/>
-    <col customWidth="1" max="4" min="4" width="14"/>
-    <col customWidth="1" max="5" min="5" width="14"/>
-    <col customWidth="1" max="6" min="6" width="14"/>
-    <col customWidth="1" max="7" min="7" width="20"/>
-    <col customWidth="1" max="8" min="8" width="18"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -588,6 +603,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
@@ -830,6 +846,7 @@
       <c r="G23" s="6" t="n"/>
       <c r="H23" s="6" t="n"/>
     </row>
+    <row r="24"/>
     <row r="25">
       <c r="A25" s="9" t="inlineStr">
         <is>
@@ -849,11 +866,19 @@
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation allowBlank="1" showDropDown="0" showErrorMessage="0" showInputMessage="0" sqref="C4 C5 C6 C7 C8 C9 C10 C11 C12 C13 C14 C15 C16 C17 C18 C19 C20 C21 C22 C23" type="list">
+    <dataValidation sqref="C4 C5 C6 C7 C8 C9 C10 C11 C12 C13 C14 C15 C16 C17 C18 C19 C20 C21 C22 C23" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Manipulador alimentos,APPCC básico,APPCC avanzado,Alérgenos,Primeros auxilios,Prevención riesgos,Atención al cliente,Otro"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
-  <pageSetup orientation="landscape"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
--- a/astro-site/public/dl/pack-appcc/BONUS-01-registro-formacion.xlsx
+++ b/astro-site/public/dl/pack-appcc/BONUS-01-registro-formacion.xlsx
@@ -10,7 +10,11 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Formación Personal" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Instrucciones'!$A$1:$B$29</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'Formación Personal'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'Formación Personal'!$A$1:$K$53</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -20,7 +24,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="DD/MM/YYYY"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="15">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -66,8 +70,35 @@
       <color rgb="00999999"/>
       <sz val="9"/>
     </font>
+    <font>
+      <b val="1"/>
+      <sz val="16"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <sz val="9"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="18"/>
+    </font>
+    <font>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -86,8 +117,18 @@
         <bgColor rgb="00E8F5E9"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="002D2D2D"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8F5E9"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -109,11 +150,25 @@
         <color rgb="00E0E0E0"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D0D0D0"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D0D0D0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D0D0D0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D0D0D0"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -132,10 +187,96 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="2" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="5" borderId="2" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="5" borderId="2" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="1" fontId="6" fillId="5" borderId="2" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="2" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="5" borderId="2" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="11" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
+  <dxfs count="3">
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="009C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00FFC7CE"/>
+          <bgColor rgb="00FFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="009C6500"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00FFEB9C"/>
+          <bgColor rgb="00FFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="00006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00C6EFCE"/>
+          <bgColor rgb="00C6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
@@ -498,24 +639,24 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:B29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
-    <col width="80" customWidth="1" min="2" max="2"/>
+    <col width="95" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1"/>
-    <row r="2">
-      <c r="B2" s="1" t="inlineStr">
-        <is>
-          <t>BONUS: Registro de Formación en Seguridad Alimentaria</t>
+    <row r="2" ht="26" customHeight="1">
+      <c r="B2" s="10" t="inlineStr">
+        <is>
+          <t>BONUS — Registro de Formación en Seguridad Alimentaria</t>
         </is>
       </c>
     </row>
     <row r="3"/>
     <row r="4">
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" s="11" t="inlineStr">
         <is>
           <t>Cómo usar esta plantilla</t>
         </is>
@@ -523,47 +664,127 @@
     </row>
     <row r="5"/>
     <row r="6">
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>▸ Registra TODA la formación del personal en seguridad alimentaria</t>
+      <c r="B6" s="12" t="inlineStr">
+        <is>
+          <t>▸ Una línea por empleado y formación. Registra TODA la formación en seguridad alimentaria: higiene, APPCC, alérgenos, limpieza, primeros auxilios.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>▸ Incluye: manipulador de alimentos, APPCC, alérgenos, primeros auxilios</t>
+      <c r="B7" s="12" t="inlineStr">
+        <is>
+          <t>▸ Rellena «Válido hasta» con la fecha de reciclaje que fije tu plan de formación. Es el dato que convierte la tabla en un aviso: la columna «Estado» se calcula sola.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>▸ El inspector puede pedir este registro en cualquier inspección</t>
-        </is>
-      </c>
-    </row>
-    <row r="9"/>
+      <c r="B8" s="12" t="inlineStr">
+        <is>
+          <t>▸ Estados: VIGENTE (verde), RENOVAR (ámbar, quedan menos de 60 días) y CADUCADO (rojo). Debajo de la tabla hay dos contadores.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="12" t="inlineStr">
+        <is>
+          <t>▸ Pide la FIRMA del empleado: es lo que acredita que recibió la formación.</t>
+        </is>
+      </c>
+    </row>
     <row r="10">
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>— Pack de Plantillas APPCC · AI Chef Pro · aichef.pro</t>
+      <c r="B10" s="12" t="inlineStr">
+        <is>
+          <t>▸ Guarda una copia de cada certificado junto con este registro. El inspector puede pedir los dos.</t>
         </is>
       </c>
     </row>
     <row r="11"/>
     <row r="12">
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>Versión 1.1 · agosto 2026 · aichef.pro/pack-appcc · info@aichef.pro</t>
+      <c r="B12" s="11" t="inlineStr">
+        <is>
+          <t>Qué exige la normativa</t>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
+    <row r="14">
+      <c r="B14" s="12" t="inlineStr">
+        <is>
+          <t>El carné oficial de manipulador de alimentos se suprimió con el RD 109/2010. Desde entonces la obligación es del operador: garantizar que quien manipula alimentos ha recibido formación en higiene alimentaria adecuada a su puesto y poder demostrarlo (Reg. (CE) 852/2004, Anexo II, Cap. XII).</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="12" t="inlineStr">
+        <is>
+          <t>▸ La norma no fija un plazo de caducidad ni una entidad obligatoria: lo fija tu plan de formación. Lo habitual es reciclar cada 2-4 años y siempre que cambien los procesos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="12" t="inlineStr">
+        <is>
+          <t>▸ La formación en alérgenos es exigible desde el Reg. (UE) 1169/2011: quien atiende en sala también tiene que saber responder.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17"/>
+    <row r="18">
+      <c r="B18" s="11" t="inlineStr">
+        <is>
+          <t>Nota sobre la fecha de hoy</t>
+        </is>
+      </c>
+    </row>
+    <row r="19"/>
+    <row r="20">
+      <c r="B20" s="12" t="inlineStr">
+        <is>
+          <t>La columna «Estado» usa la función TODAY(), así que se actualiza sola cada vez que abres el fichero con Excel, LibreOffice o Google Sheets. Si lo miras en un visor que no recalcula (la vista previa del móvil, por ejemplo), verás el valor del día en que se generó la plantilla.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21"/>
+    <row r="22">
+      <c r="B22" s="11" t="inlineStr">
+        <is>
+          <t>Frecuencia y archivo</t>
+        </is>
+      </c>
+    </row>
+    <row r="23"/>
+    <row r="24">
+      <c r="B24" s="12" t="inlineStr">
+        <is>
+          <t>▸ Revisa el registro al menos una vez al trimestre y cada vez que entre alguien nuevo. La hoja trae 40 filas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="12" t="inlineStr">
+        <is>
+          <t>▸ Conservar al menos 2 años (trazabilidad y proveedores: 5); el Reg. (CE) 178/2002 exige trazabilidad pero no fija plazo — consulta la guía de prácticas correctas de higiene de tu comunidad autónoma.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26"/>
+    <row r="27">
+      <c r="B27" s="11" t="inlineStr">
+        <is>
+          <t>— Pack de Plantillas APPCC · AI Chef Pro · aichef.pro</t>
+        </is>
+      </c>
+    </row>
+    <row r="28"/>
+    <row r="29">
+      <c r="B29" s="11" t="inlineStr">
+        <is>
+          <t>Versión 2.0 · agosto 2026 · aichef.pro/pack-appcc · info@aichef.pro</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="B2"/>
-  </mergeCells>
-  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageMargins left="0.55" right="0.55" top="0.55" bottom="0.55" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader/>
@@ -583,294 +804,922 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H26"/>
+  <dimension ref="A1:K53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
     <col width="30" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="7" max="7"/>
     <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="20" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="13" t="inlineStr">
         <is>
           <t>BONUS — Registro de Formación en Seguridad Alimentaria</t>
         </is>
       </c>
     </row>
-    <row r="2"/>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Establecimiento: ________________________________    Responsable: _________________________________</t>
+        </is>
+      </c>
+    </row>
     <row r="3">
-      <c r="A3" s="5" t="inlineStr">
-        <is>
-          <t>Nombre Empleado</t>
-        </is>
-      </c>
-      <c r="B3" s="5" t="inlineStr">
+      <c r="A3" s="5" t="n"/>
+      <c r="B3" s="5" t="n"/>
+      <c r="C3" s="5" t="n"/>
+      <c r="D3" s="5" t="n"/>
+      <c r="E3" s="5" t="n"/>
+      <c r="F3" s="5" t="n"/>
+      <c r="G3" s="5" t="n"/>
+      <c r="H3" s="5" t="n"/>
+    </row>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="14" t="inlineStr">
+        <is>
+          <t>Nombre del empleado</t>
+        </is>
+      </c>
+      <c r="B4" s="14" t="inlineStr">
         <is>
           <t>Puesto</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
-        <is>
-          <t>Formación Recibida</t>
-        </is>
-      </c>
-      <c r="D3" s="5" t="inlineStr">
-        <is>
-          <t>Fecha Inicio</t>
-        </is>
-      </c>
-      <c r="E3" s="5" t="inlineStr">
-        <is>
-          <t>Fecha Fin</t>
-        </is>
-      </c>
-      <c r="F3" s="5" t="inlineStr">
+      <c r="C4" s="14" t="inlineStr">
+        <is>
+          <t>Formación recibida</t>
+        </is>
+      </c>
+      <c r="D4" s="15" t="inlineStr">
+        <is>
+          <t>Fecha inicio</t>
+        </is>
+      </c>
+      <c r="E4" s="15" t="inlineStr">
+        <is>
+          <t>Fecha fin</t>
+        </is>
+      </c>
+      <c r="F4" s="14" t="inlineStr">
         <is>
           <t>Duración (h)</t>
         </is>
       </c>
-      <c r="G3" s="5" t="inlineStr">
-        <is>
-          <t>Entidad Formadora</t>
-        </is>
-      </c>
-      <c r="H3" s="5" t="inlineStr">
-        <is>
-          <t>Nº Certificado</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="6" t="n"/>
-      <c r="B4" s="6" t="n"/>
-      <c r="C4" s="6" t="n"/>
-      <c r="D4" s="7" t="n"/>
-      <c r="E4" s="7" t="n"/>
-      <c r="F4" s="8" t="n"/>
-      <c r="G4" s="6" t="n"/>
-      <c r="H4" s="6" t="n"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="6" t="n"/>
-      <c r="B5" s="6" t="n"/>
-      <c r="C5" s="6" t="n"/>
-      <c r="D5" s="7" t="n"/>
-      <c r="E5" s="7" t="n"/>
-      <c r="F5" s="8" t="n"/>
-      <c r="G5" s="6" t="n"/>
-      <c r="H5" s="6" t="n"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="6" t="n"/>
-      <c r="B6" s="6" t="n"/>
-      <c r="C6" s="6" t="n"/>
-      <c r="D6" s="7" t="n"/>
-      <c r="E6" s="7" t="n"/>
-      <c r="F6" s="8" t="n"/>
-      <c r="G6" s="6" t="n"/>
-      <c r="H6" s="6" t="n"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="6" t="n"/>
-      <c r="B7" s="6" t="n"/>
-      <c r="C7" s="6" t="n"/>
-      <c r="D7" s="7" t="n"/>
-      <c r="E7" s="7" t="n"/>
-      <c r="F7" s="8" t="n"/>
-      <c r="G7" s="6" t="n"/>
-      <c r="H7" s="6" t="n"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="6" t="n"/>
-      <c r="B8" s="6" t="n"/>
-      <c r="C8" s="6" t="n"/>
-      <c r="D8" s="7" t="n"/>
-      <c r="E8" s="7" t="n"/>
-      <c r="F8" s="8" t="n"/>
-      <c r="G8" s="6" t="n"/>
-      <c r="H8" s="6" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="6" t="n"/>
-      <c r="B9" s="6" t="n"/>
-      <c r="C9" s="6" t="n"/>
-      <c r="D9" s="7" t="n"/>
-      <c r="E9" s="7" t="n"/>
-      <c r="F9" s="8" t="n"/>
-      <c r="G9" s="6" t="n"/>
-      <c r="H9" s="6" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="6" t="n"/>
-      <c r="B10" s="6" t="n"/>
-      <c r="C10" s="6" t="n"/>
-      <c r="D10" s="7" t="n"/>
-      <c r="E10" s="7" t="n"/>
-      <c r="F10" s="8" t="n"/>
-      <c r="G10" s="6" t="n"/>
-      <c r="H10" s="6" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="6" t="n"/>
-      <c r="B11" s="6" t="n"/>
-      <c r="C11" s="6" t="n"/>
-      <c r="D11" s="7" t="n"/>
-      <c r="E11" s="7" t="n"/>
-      <c r="F11" s="8" t="n"/>
-      <c r="G11" s="6" t="n"/>
-      <c r="H11" s="6" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="6" t="n"/>
-      <c r="B12" s="6" t="n"/>
-      <c r="C12" s="6" t="n"/>
-      <c r="D12" s="7" t="n"/>
-      <c r="E12" s="7" t="n"/>
-      <c r="F12" s="8" t="n"/>
-      <c r="G12" s="6" t="n"/>
-      <c r="H12" s="6" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="6" t="n"/>
-      <c r="B13" s="6" t="n"/>
-      <c r="C13" s="6" t="n"/>
-      <c r="D13" s="7" t="n"/>
-      <c r="E13" s="7" t="n"/>
-      <c r="F13" s="8" t="n"/>
-      <c r="G13" s="6" t="n"/>
-      <c r="H13" s="6" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="6" t="n"/>
-      <c r="B14" s="6" t="n"/>
-      <c r="C14" s="6" t="n"/>
-      <c r="D14" s="7" t="n"/>
-      <c r="E14" s="7" t="n"/>
-      <c r="F14" s="8" t="n"/>
-      <c r="G14" s="6" t="n"/>
-      <c r="H14" s="6" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="6" t="n"/>
-      <c r="B15" s="6" t="n"/>
-      <c r="C15" s="6" t="n"/>
-      <c r="D15" s="7" t="n"/>
-      <c r="E15" s="7" t="n"/>
-      <c r="F15" s="8" t="n"/>
-      <c r="G15" s="6" t="n"/>
-      <c r="H15" s="6" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="6" t="n"/>
-      <c r="B16" s="6" t="n"/>
-      <c r="C16" s="6" t="n"/>
-      <c r="D16" s="7" t="n"/>
-      <c r="E16" s="7" t="n"/>
-      <c r="F16" s="8" t="n"/>
-      <c r="G16" s="6" t="n"/>
-      <c r="H16" s="6" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="6" t="n"/>
-      <c r="B17" s="6" t="n"/>
-      <c r="C17" s="6" t="n"/>
-      <c r="D17" s="7" t="n"/>
-      <c r="E17" s="7" t="n"/>
-      <c r="F17" s="8" t="n"/>
-      <c r="G17" s="6" t="n"/>
-      <c r="H17" s="6" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="6" t="n"/>
-      <c r="B18" s="6" t="n"/>
-      <c r="C18" s="6" t="n"/>
-      <c r="D18" s="7" t="n"/>
-      <c r="E18" s="7" t="n"/>
-      <c r="F18" s="8" t="n"/>
-      <c r="G18" s="6" t="n"/>
-      <c r="H18" s="6" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="6" t="n"/>
-      <c r="B19" s="6" t="n"/>
-      <c r="C19" s="6" t="n"/>
-      <c r="D19" s="7" t="n"/>
-      <c r="E19" s="7" t="n"/>
-      <c r="F19" s="8" t="n"/>
-      <c r="G19" s="6" t="n"/>
-      <c r="H19" s="6" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="6" t="n"/>
-      <c r="B20" s="6" t="n"/>
-      <c r="C20" s="6" t="n"/>
-      <c r="D20" s="7" t="n"/>
-      <c r="E20" s="7" t="n"/>
-      <c r="F20" s="8" t="n"/>
-      <c r="G20" s="6" t="n"/>
-      <c r="H20" s="6" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="6" t="n"/>
-      <c r="B21" s="6" t="n"/>
-      <c r="C21" s="6" t="n"/>
-      <c r="D21" s="7" t="n"/>
-      <c r="E21" s="7" t="n"/>
-      <c r="F21" s="8" t="n"/>
-      <c r="G21" s="6" t="n"/>
-      <c r="H21" s="6" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="6" t="n"/>
-      <c r="B22" s="6" t="n"/>
-      <c r="C22" s="6" t="n"/>
-      <c r="D22" s="7" t="n"/>
-      <c r="E22" s="7" t="n"/>
-      <c r="F22" s="8" t="n"/>
-      <c r="G22" s="6" t="n"/>
-      <c r="H22" s="6" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="6" t="n"/>
-      <c r="B23" s="6" t="n"/>
-      <c r="C23" s="6" t="n"/>
-      <c r="D23" s="7" t="n"/>
-      <c r="E23" s="7" t="n"/>
-      <c r="F23" s="8" t="n"/>
-      <c r="G23" s="6" t="n"/>
-      <c r="H23" s="6" t="n"/>
-    </row>
-    <row r="24"/>
-    <row r="25">
-      <c r="A25" s="9" t="inlineStr">
-        <is>
-          <t>Todo el personal que manipula alimentos debe tener formación acreditada vigente.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="9" t="inlineStr">
+      <c r="G4" s="14" t="inlineStr">
+        <is>
+          <t>Entidad formadora</t>
+        </is>
+      </c>
+      <c r="H4" s="14" t="inlineStr">
+        <is>
+          <t>Nº certificado</t>
+        </is>
+      </c>
+      <c r="I4" s="14" t="inlineStr">
+        <is>
+          <t>Válido hasta</t>
+        </is>
+      </c>
+      <c r="J4" s="14" t="inlineStr">
+        <is>
+          <t>Estado</t>
+        </is>
+      </c>
+      <c r="K4" s="14" t="inlineStr">
+        <is>
+          <t>Firma del empleado</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="20" customHeight="1">
+      <c r="A5" s="16" t="inlineStr">
+        <is>
+          <t>Ana Ruiz (ejemplo)</t>
+        </is>
+      </c>
+      <c r="B5" s="17" t="inlineStr">
+        <is>
+          <t>Jefa de cocina</t>
+        </is>
+      </c>
+      <c r="C5" s="16" t="inlineStr">
+        <is>
+          <t>Higiene alimentaria (manipulación de alimentos)</t>
+        </is>
+      </c>
+      <c r="D5" s="18" t="n">
+        <v>46061</v>
+      </c>
+      <c r="E5" s="18" t="n">
+        <v>46061</v>
+      </c>
+      <c r="F5" s="19" t="n">
+        <v>6</v>
+      </c>
+      <c r="G5" s="16" t="inlineStr">
+        <is>
+          <t>Formación Hostelera Norte S.L.</t>
+        </is>
+      </c>
+      <c r="H5" s="17" t="inlineStr">
+        <is>
+          <t>CERT-2026-0039</t>
+        </is>
+      </c>
+      <c r="I5" s="20">
+        <f>TODAY()+900</f>
+        <v>47156.0</v>
+      </c>
+      <c r="J5" s="21" t="str">
+        <f>IF(NOT(ISNUMBER($I5)),"",IF($I5&lt;TODAY(),"CADUCADO",IF($I5-TODAY()&lt;60,"RENOVAR","VIGENTE")))</f>
+        <v>VIGENTE</v>
+      </c>
+      <c r="K5" s="22" t="inlineStr">
+        <is>
+          <t>A.R.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="16" t="inlineStr">
+        <is>
+          <t>Marcos Sáez (ejemplo)</t>
+        </is>
+      </c>
+      <c r="B6" s="17" t="inlineStr">
+        <is>
+          <t>Cocinero</t>
+        </is>
+      </c>
+      <c r="C6" s="16" t="inlineStr">
+        <is>
+          <t>Alérgenos e información al consumidor</t>
+        </is>
+      </c>
+      <c r="D6" s="18" t="n">
+        <v>45191</v>
+      </c>
+      <c r="E6" s="18" t="n">
+        <v>45191</v>
+      </c>
+      <c r="F6" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="G6" s="16" t="inlineStr">
+        <is>
+          <t>Formación Hostelera Norte S.L.</t>
+        </is>
+      </c>
+      <c r="H6" s="17" t="inlineStr">
+        <is>
+          <t>CERT-2023-0265</t>
+        </is>
+      </c>
+      <c r="I6" s="20">
+        <f>TODAY()+30</f>
+        <v>46286.0</v>
+      </c>
+      <c r="J6" s="21" t="str">
+        <f>IF(NOT(ISNUMBER($I6)),"",IF($I6&lt;TODAY(),"CADUCADO",IF($I6-TODAY()&lt;60,"RENOVAR","VIGENTE")))</f>
+        <v>RENOVAR</v>
+      </c>
+      <c r="K6" s="22" t="inlineStr">
+        <is>
+          <t>M.S.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="20" customHeight="1">
+      <c r="A7" s="16" t="inlineStr">
+        <is>
+          <t>Lucía Prat (ejemplo)</t>
+        </is>
+      </c>
+      <c r="B7" s="17" t="inlineStr">
+        <is>
+          <t>Camarera</t>
+        </is>
+      </c>
+      <c r="C7" s="16" t="inlineStr">
+        <is>
+          <t>Higiene alimentaria (manipulación de alimentos)</t>
+        </is>
+      </c>
+      <c r="D7" s="18" t="n">
+        <v>45101</v>
+      </c>
+      <c r="E7" s="18" t="n">
+        <v>45101</v>
+      </c>
+      <c r="F7" s="19" t="n">
+        <v>6</v>
+      </c>
+      <c r="G7" s="16" t="inlineStr">
+        <is>
+          <t>Aula Gastro Formación</t>
+        </is>
+      </c>
+      <c r="H7" s="17" t="inlineStr">
+        <is>
+          <t>CERT-2023-0175</t>
+        </is>
+      </c>
+      <c r="I7" s="20">
+        <f>TODAY()-60</f>
+        <v>46196.0</v>
+      </c>
+      <c r="J7" s="21" t="str">
+        <f>IF(NOT(ISNUMBER($I7)),"",IF($I7&lt;TODAY(),"CADUCADO",IF($I7-TODAY()&lt;60,"RENOVAR","VIGENTE")))</f>
+        <v>CADUCADO</v>
+      </c>
+      <c r="K7" s="22" t="inlineStr">
+        <is>
+          <t>L.P.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="20" customHeight="1">
+      <c r="A8" s="16" t="n"/>
+      <c r="B8" s="17" t="n"/>
+      <c r="C8" s="16" t="n"/>
+      <c r="D8" s="18" t="n"/>
+      <c r="E8" s="18" t="n"/>
+      <c r="F8" s="19" t="n"/>
+      <c r="G8" s="16" t="n"/>
+      <c r="H8" s="17" t="n"/>
+      <c r="I8" s="20" t="n"/>
+      <c r="J8" s="21">
+        <f>IF(NOT(ISNUMBER($I8)),"",IF($I8&lt;TODAY(),"CADUCADO",IF($I8-TODAY()&lt;60,"RENOVAR","VIGENTE")))</f>
+      </c>
+      <c r="K8" s="22" t="n"/>
+    </row>
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="16" t="n"/>
+      <c r="B9" s="17" t="n"/>
+      <c r="C9" s="16" t="n"/>
+      <c r="D9" s="18" t="n"/>
+      <c r="E9" s="18" t="n"/>
+      <c r="F9" s="19" t="n"/>
+      <c r="G9" s="16" t="n"/>
+      <c r="H9" s="17" t="n"/>
+      <c r="I9" s="20" t="n"/>
+      <c r="J9" s="21">
+        <f>IF(NOT(ISNUMBER($I9)),"",IF($I9&lt;TODAY(),"CADUCADO",IF($I9-TODAY()&lt;60,"RENOVAR","VIGENTE")))</f>
+      </c>
+      <c r="K9" s="22" t="n"/>
+    </row>
+    <row r="10" ht="20" customHeight="1">
+      <c r="A10" s="16" t="n"/>
+      <c r="B10" s="17" t="n"/>
+      <c r="C10" s="16" t="n"/>
+      <c r="D10" s="18" t="n"/>
+      <c r="E10" s="18" t="n"/>
+      <c r="F10" s="19" t="n"/>
+      <c r="G10" s="16" t="n"/>
+      <c r="H10" s="17" t="n"/>
+      <c r="I10" s="20" t="n"/>
+      <c r="J10" s="21">
+        <f>IF(NOT(ISNUMBER($I10)),"",IF($I10&lt;TODAY(),"CADUCADO",IF($I10-TODAY()&lt;60,"RENOVAR","VIGENTE")))</f>
+      </c>
+      <c r="K10" s="22" t="n"/>
+    </row>
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="16" t="n"/>
+      <c r="B11" s="17" t="n"/>
+      <c r="C11" s="16" t="n"/>
+      <c r="D11" s="18" t="n"/>
+      <c r="E11" s="18" t="n"/>
+      <c r="F11" s="19" t="n"/>
+      <c r="G11" s="16" t="n"/>
+      <c r="H11" s="17" t="n"/>
+      <c r="I11" s="20" t="n"/>
+      <c r="J11" s="21">
+        <f>IF(NOT(ISNUMBER($I11)),"",IF($I11&lt;TODAY(),"CADUCADO",IF($I11-TODAY()&lt;60,"RENOVAR","VIGENTE")))</f>
+      </c>
+      <c r="K11" s="22" t="n"/>
+    </row>
+    <row r="12" ht="20" customHeight="1">
+      <c r="A12" s="16" t="n"/>
+      <c r="B12" s="17" t="n"/>
+      <c r="C12" s="16" t="n"/>
+      <c r="D12" s="18" t="n"/>
+      <c r="E12" s="18" t="n"/>
+      <c r="F12" s="19" t="n"/>
+      <c r="G12" s="16" t="n"/>
+      <c r="H12" s="17" t="n"/>
+      <c r="I12" s="20" t="n"/>
+      <c r="J12" s="21">
+        <f>IF(NOT(ISNUMBER($I12)),"",IF($I12&lt;TODAY(),"CADUCADO",IF($I12-TODAY()&lt;60,"RENOVAR","VIGENTE")))</f>
+      </c>
+      <c r="K12" s="22" t="n"/>
+    </row>
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="16" t="n"/>
+      <c r="B13" s="17" t="n"/>
+      <c r="C13" s="16" t="n"/>
+      <c r="D13" s="18" t="n"/>
+      <c r="E13" s="18" t="n"/>
+      <c r="F13" s="19" t="n"/>
+      <c r="G13" s="16" t="n"/>
+      <c r="H13" s="17" t="n"/>
+      <c r="I13" s="20" t="n"/>
+      <c r="J13" s="21">
+        <f>IF(NOT(ISNUMBER($I13)),"",IF($I13&lt;TODAY(),"CADUCADO",IF($I13-TODAY()&lt;60,"RENOVAR","VIGENTE")))</f>
+      </c>
+      <c r="K13" s="22" t="n"/>
+    </row>
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" s="16" t="n"/>
+      <c r="B14" s="17" t="n"/>
+      <c r="C14" s="16" t="n"/>
+      <c r="D14" s="18" t="n"/>
+      <c r="E14" s="18" t="n"/>
+      <c r="F14" s="19" t="n"/>
+      <c r="G14" s="16" t="n"/>
+      <c r="H14" s="17" t="n"/>
+      <c r="I14" s="20" t="n"/>
+      <c r="J14" s="21">
+        <f>IF(NOT(ISNUMBER($I14)),"",IF($I14&lt;TODAY(),"CADUCADO",IF($I14-TODAY()&lt;60,"RENOVAR","VIGENTE")))</f>
+      </c>
+      <c r="K14" s="22" t="n"/>
+    </row>
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" s="16" t="n"/>
+      <c r="B15" s="17" t="n"/>
+      <c r="C15" s="16" t="n"/>
+      <c r="D15" s="18" t="n"/>
+      <c r="E15" s="18" t="n"/>
+      <c r="F15" s="19" t="n"/>
+      <c r="G15" s="16" t="n"/>
+      <c r="H15" s="17" t="n"/>
+      <c r="I15" s="20" t="n"/>
+      <c r="J15" s="21">
+        <f>IF(NOT(ISNUMBER($I15)),"",IF($I15&lt;TODAY(),"CADUCADO",IF($I15-TODAY()&lt;60,"RENOVAR","VIGENTE")))</f>
+      </c>
+      <c r="K15" s="22" t="n"/>
+    </row>
+    <row r="16" ht="20" customHeight="1">
+      <c r="A16" s="16" t="n"/>
+      <c r="B16" s="17" t="n"/>
+      <c r="C16" s="16" t="n"/>
+      <c r="D16" s="18" t="n"/>
+      <c r="E16" s="18" t="n"/>
+      <c r="F16" s="19" t="n"/>
+      <c r="G16" s="16" t="n"/>
+      <c r="H16" s="17" t="n"/>
+      <c r="I16" s="20" t="n"/>
+      <c r="J16" s="21">
+        <f>IF(NOT(ISNUMBER($I16)),"",IF($I16&lt;TODAY(),"CADUCADO",IF($I16-TODAY()&lt;60,"RENOVAR","VIGENTE")))</f>
+      </c>
+      <c r="K16" s="22" t="n"/>
+    </row>
+    <row r="17" ht="20" customHeight="1">
+      <c r="A17" s="16" t="n"/>
+      <c r="B17" s="17" t="n"/>
+      <c r="C17" s="16" t="n"/>
+      <c r="D17" s="18" t="n"/>
+      <c r="E17" s="18" t="n"/>
+      <c r="F17" s="19" t="n"/>
+      <c r="G17" s="16" t="n"/>
+      <c r="H17" s="17" t="n"/>
+      <c r="I17" s="20" t="n"/>
+      <c r="J17" s="21">
+        <f>IF(NOT(ISNUMBER($I17)),"",IF($I17&lt;TODAY(),"CADUCADO",IF($I17-TODAY()&lt;60,"RENOVAR","VIGENTE")))</f>
+      </c>
+      <c r="K17" s="22" t="n"/>
+    </row>
+    <row r="18" ht="20" customHeight="1">
+      <c r="A18" s="16" t="n"/>
+      <c r="B18" s="17" t="n"/>
+      <c r="C18" s="16" t="n"/>
+      <c r="D18" s="18" t="n"/>
+      <c r="E18" s="18" t="n"/>
+      <c r="F18" s="19" t="n"/>
+      <c r="G18" s="16" t="n"/>
+      <c r="H18" s="17" t="n"/>
+      <c r="I18" s="20" t="n"/>
+      <c r="J18" s="21">
+        <f>IF(NOT(ISNUMBER($I18)),"",IF($I18&lt;TODAY(),"CADUCADO",IF($I18-TODAY()&lt;60,"RENOVAR","VIGENTE")))</f>
+      </c>
+      <c r="K18" s="22" t="n"/>
+    </row>
+    <row r="19" ht="20" customHeight="1">
+      <c r="A19" s="16" t="n"/>
+      <c r="B19" s="17" t="n"/>
+      <c r="C19" s="16" t="n"/>
+      <c r="D19" s="18" t="n"/>
+      <c r="E19" s="18" t="n"/>
+      <c r="F19" s="19" t="n"/>
+      <c r="G19" s="16" t="n"/>
+      <c r="H19" s="17" t="n"/>
+      <c r="I19" s="20" t="n"/>
+      <c r="J19" s="21">
+        <f>IF(NOT(ISNUMBER($I19)),"",IF($I19&lt;TODAY(),"CADUCADO",IF($I19-TODAY()&lt;60,"RENOVAR","VIGENTE")))</f>
+      </c>
+      <c r="K19" s="22" t="n"/>
+    </row>
+    <row r="20" ht="20" customHeight="1">
+      <c r="A20" s="16" t="n"/>
+      <c r="B20" s="17" t="n"/>
+      <c r="C20" s="16" t="n"/>
+      <c r="D20" s="18" t="n"/>
+      <c r="E20" s="18" t="n"/>
+      <c r="F20" s="19" t="n"/>
+      <c r="G20" s="16" t="n"/>
+      <c r="H20" s="17" t="n"/>
+      <c r="I20" s="20" t="n"/>
+      <c r="J20" s="21">
+        <f>IF(NOT(ISNUMBER($I20)),"",IF($I20&lt;TODAY(),"CADUCADO",IF($I20-TODAY()&lt;60,"RENOVAR","VIGENTE")))</f>
+      </c>
+      <c r="K20" s="22" t="n"/>
+    </row>
+    <row r="21" ht="20" customHeight="1">
+      <c r="A21" s="16" t="n"/>
+      <c r="B21" s="17" t="n"/>
+      <c r="C21" s="16" t="n"/>
+      <c r="D21" s="18" t="n"/>
+      <c r="E21" s="18" t="n"/>
+      <c r="F21" s="19" t="n"/>
+      <c r="G21" s="16" t="n"/>
+      <c r="H21" s="17" t="n"/>
+      <c r="I21" s="20" t="n"/>
+      <c r="J21" s="21">
+        <f>IF(NOT(ISNUMBER($I21)),"",IF($I21&lt;TODAY(),"CADUCADO",IF($I21-TODAY()&lt;60,"RENOVAR","VIGENTE")))</f>
+      </c>
+      <c r="K21" s="22" t="n"/>
+    </row>
+    <row r="22" ht="20" customHeight="1">
+      <c r="A22" s="16" t="n"/>
+      <c r="B22" s="17" t="n"/>
+      <c r="C22" s="16" t="n"/>
+      <c r="D22" s="18" t="n"/>
+      <c r="E22" s="18" t="n"/>
+      <c r="F22" s="19" t="n"/>
+      <c r="G22" s="16" t="n"/>
+      <c r="H22" s="17" t="n"/>
+      <c r="I22" s="20" t="n"/>
+      <c r="J22" s="21">
+        <f>IF(NOT(ISNUMBER($I22)),"",IF($I22&lt;TODAY(),"CADUCADO",IF($I22-TODAY()&lt;60,"RENOVAR","VIGENTE")))</f>
+      </c>
+      <c r="K22" s="22" t="n"/>
+    </row>
+    <row r="23" ht="20" customHeight="1">
+      <c r="A23" s="16" t="n"/>
+      <c r="B23" s="17" t="n"/>
+      <c r="C23" s="16" t="n"/>
+      <c r="D23" s="18" t="n"/>
+      <c r="E23" s="18" t="n"/>
+      <c r="F23" s="19" t="n"/>
+      <c r="G23" s="16" t="n"/>
+      <c r="H23" s="17" t="n"/>
+      <c r="I23" s="20" t="n"/>
+      <c r="J23" s="21">
+        <f>IF(NOT(ISNUMBER($I23)),"",IF($I23&lt;TODAY(),"CADUCADO",IF($I23-TODAY()&lt;60,"RENOVAR","VIGENTE")))</f>
+      </c>
+      <c r="K23" s="22" t="n"/>
+    </row>
+    <row r="24" ht="20" customHeight="1">
+      <c r="A24" s="16" t="n"/>
+      <c r="B24" s="17" t="n"/>
+      <c r="C24" s="16" t="n"/>
+      <c r="D24" s="18" t="n"/>
+      <c r="E24" s="18" t="n"/>
+      <c r="F24" s="19" t="n"/>
+      <c r="G24" s="16" t="n"/>
+      <c r="H24" s="17" t="n"/>
+      <c r="I24" s="20" t="n"/>
+      <c r="J24" s="21">
+        <f>IF(NOT(ISNUMBER($I24)),"",IF($I24&lt;TODAY(),"CADUCADO",IF($I24-TODAY()&lt;60,"RENOVAR","VIGENTE")))</f>
+      </c>
+      <c r="K24" s="22" t="n"/>
+    </row>
+    <row r="25" ht="20" customHeight="1">
+      <c r="A25" s="16" t="n"/>
+      <c r="B25" s="17" t="n"/>
+      <c r="C25" s="16" t="n"/>
+      <c r="D25" s="18" t="n"/>
+      <c r="E25" s="18" t="n"/>
+      <c r="F25" s="19" t="n"/>
+      <c r="G25" s="16" t="n"/>
+      <c r="H25" s="17" t="n"/>
+      <c r="I25" s="20" t="n"/>
+      <c r="J25" s="21">
+        <f>IF(NOT(ISNUMBER($I25)),"",IF($I25&lt;TODAY(),"CADUCADO",IF($I25-TODAY()&lt;60,"RENOVAR","VIGENTE")))</f>
+      </c>
+      <c r="K25" s="22" t="n"/>
+    </row>
+    <row r="26" ht="20" customHeight="1">
+      <c r="A26" s="16" t="n"/>
+      <c r="B26" s="17" t="n"/>
+      <c r="C26" s="16" t="n"/>
+      <c r="D26" s="18" t="n"/>
+      <c r="E26" s="18" t="n"/>
+      <c r="F26" s="19" t="n"/>
+      <c r="G26" s="16" t="n"/>
+      <c r="H26" s="17" t="n"/>
+      <c r="I26" s="20" t="n"/>
+      <c r="J26" s="21">
+        <f>IF(NOT(ISNUMBER($I26)),"",IF($I26&lt;TODAY(),"CADUCADO",IF($I26-TODAY()&lt;60,"RENOVAR","VIGENTE")))</f>
+      </c>
+      <c r="K26" s="22" t="n"/>
+    </row>
+    <row r="27" ht="20" customHeight="1">
+      <c r="A27" s="16" t="n"/>
+      <c r="B27" s="17" t="n"/>
+      <c r="C27" s="16" t="n"/>
+      <c r="D27" s="18" t="n"/>
+      <c r="E27" s="18" t="n"/>
+      <c r="F27" s="19" t="n"/>
+      <c r="G27" s="16" t="n"/>
+      <c r="H27" s="17" t="n"/>
+      <c r="I27" s="20" t="n"/>
+      <c r="J27" s="21">
+        <f>IF(NOT(ISNUMBER($I27)),"",IF($I27&lt;TODAY(),"CADUCADO",IF($I27-TODAY()&lt;60,"RENOVAR","VIGENTE")))</f>
+      </c>
+      <c r="K27" s="22" t="n"/>
+    </row>
+    <row r="28" ht="20" customHeight="1">
+      <c r="A28" s="16" t="n"/>
+      <c r="B28" s="17" t="n"/>
+      <c r="C28" s="16" t="n"/>
+      <c r="D28" s="18" t="n"/>
+      <c r="E28" s="18" t="n"/>
+      <c r="F28" s="19" t="n"/>
+      <c r="G28" s="16" t="n"/>
+      <c r="H28" s="17" t="n"/>
+      <c r="I28" s="20" t="n"/>
+      <c r="J28" s="21">
+        <f>IF(NOT(ISNUMBER($I28)),"",IF($I28&lt;TODAY(),"CADUCADO",IF($I28-TODAY()&lt;60,"RENOVAR","VIGENTE")))</f>
+      </c>
+      <c r="K28" s="22" t="n"/>
+    </row>
+    <row r="29" ht="20" customHeight="1">
+      <c r="A29" s="16" t="n"/>
+      <c r="B29" s="17" t="n"/>
+      <c r="C29" s="16" t="n"/>
+      <c r="D29" s="18" t="n"/>
+      <c r="E29" s="18" t="n"/>
+      <c r="F29" s="19" t="n"/>
+      <c r="G29" s="16" t="n"/>
+      <c r="H29" s="17" t="n"/>
+      <c r="I29" s="20" t="n"/>
+      <c r="J29" s="21">
+        <f>IF(NOT(ISNUMBER($I29)),"",IF($I29&lt;TODAY(),"CADUCADO",IF($I29-TODAY()&lt;60,"RENOVAR","VIGENTE")))</f>
+      </c>
+      <c r="K29" s="22" t="n"/>
+    </row>
+    <row r="30" ht="20" customHeight="1">
+      <c r="A30" s="16" t="n"/>
+      <c r="B30" s="17" t="n"/>
+      <c r="C30" s="16" t="n"/>
+      <c r="D30" s="18" t="n"/>
+      <c r="E30" s="18" t="n"/>
+      <c r="F30" s="19" t="n"/>
+      <c r="G30" s="16" t="n"/>
+      <c r="H30" s="17" t="n"/>
+      <c r="I30" s="20" t="n"/>
+      <c r="J30" s="21">
+        <f>IF(NOT(ISNUMBER($I30)),"",IF($I30&lt;TODAY(),"CADUCADO",IF($I30-TODAY()&lt;60,"RENOVAR","VIGENTE")))</f>
+      </c>
+      <c r="K30" s="22" t="n"/>
+    </row>
+    <row r="31" ht="20" customHeight="1">
+      <c r="A31" s="16" t="n"/>
+      <c r="B31" s="17" t="n"/>
+      <c r="C31" s="16" t="n"/>
+      <c r="D31" s="18" t="n"/>
+      <c r="E31" s="18" t="n"/>
+      <c r="F31" s="19" t="n"/>
+      <c r="G31" s="16" t="n"/>
+      <c r="H31" s="17" t="n"/>
+      <c r="I31" s="20" t="n"/>
+      <c r="J31" s="21">
+        <f>IF(NOT(ISNUMBER($I31)),"",IF($I31&lt;TODAY(),"CADUCADO",IF($I31-TODAY()&lt;60,"RENOVAR","VIGENTE")))</f>
+      </c>
+      <c r="K31" s="22" t="n"/>
+    </row>
+    <row r="32" ht="20" customHeight="1">
+      <c r="A32" s="16" t="n"/>
+      <c r="B32" s="17" t="n"/>
+      <c r="C32" s="16" t="n"/>
+      <c r="D32" s="18" t="n"/>
+      <c r="E32" s="18" t="n"/>
+      <c r="F32" s="19" t="n"/>
+      <c r="G32" s="16" t="n"/>
+      <c r="H32" s="17" t="n"/>
+      <c r="I32" s="20" t="n"/>
+      <c r="J32" s="21">
+        <f>IF(NOT(ISNUMBER($I32)),"",IF($I32&lt;TODAY(),"CADUCADO",IF($I32-TODAY()&lt;60,"RENOVAR","VIGENTE")))</f>
+      </c>
+      <c r="K32" s="22" t="n"/>
+    </row>
+    <row r="33" ht="20" customHeight="1">
+      <c r="A33" s="16" t="n"/>
+      <c r="B33" s="17" t="n"/>
+      <c r="C33" s="16" t="n"/>
+      <c r="D33" s="18" t="n"/>
+      <c r="E33" s="18" t="n"/>
+      <c r="F33" s="19" t="n"/>
+      <c r="G33" s="16" t="n"/>
+      <c r="H33" s="17" t="n"/>
+      <c r="I33" s="20" t="n"/>
+      <c r="J33" s="21">
+        <f>IF(NOT(ISNUMBER($I33)),"",IF($I33&lt;TODAY(),"CADUCADO",IF($I33-TODAY()&lt;60,"RENOVAR","VIGENTE")))</f>
+      </c>
+      <c r="K33" s="22" t="n"/>
+    </row>
+    <row r="34" ht="20" customHeight="1">
+      <c r="A34" s="16" t="n"/>
+      <c r="B34" s="17" t="n"/>
+      <c r="C34" s="16" t="n"/>
+      <c r="D34" s="18" t="n"/>
+      <c r="E34" s="18" t="n"/>
+      <c r="F34" s="19" t="n"/>
+      <c r="G34" s="16" t="n"/>
+      <c r="H34" s="17" t="n"/>
+      <c r="I34" s="20" t="n"/>
+      <c r="J34" s="21">
+        <f>IF(NOT(ISNUMBER($I34)),"",IF($I34&lt;TODAY(),"CADUCADO",IF($I34-TODAY()&lt;60,"RENOVAR","VIGENTE")))</f>
+      </c>
+      <c r="K34" s="22" t="n"/>
+    </row>
+    <row r="35" ht="20" customHeight="1">
+      <c r="A35" s="16" t="n"/>
+      <c r="B35" s="17" t="n"/>
+      <c r="C35" s="16" t="n"/>
+      <c r="D35" s="18" t="n"/>
+      <c r="E35" s="18" t="n"/>
+      <c r="F35" s="19" t="n"/>
+      <c r="G35" s="16" t="n"/>
+      <c r="H35" s="17" t="n"/>
+      <c r="I35" s="20" t="n"/>
+      <c r="J35" s="21">
+        <f>IF(NOT(ISNUMBER($I35)),"",IF($I35&lt;TODAY(),"CADUCADO",IF($I35-TODAY()&lt;60,"RENOVAR","VIGENTE")))</f>
+      </c>
+      <c r="K35" s="22" t="n"/>
+    </row>
+    <row r="36" ht="20" customHeight="1">
+      <c r="A36" s="16" t="n"/>
+      <c r="B36" s="17" t="n"/>
+      <c r="C36" s="16" t="n"/>
+      <c r="D36" s="18" t="n"/>
+      <c r="E36" s="18" t="n"/>
+      <c r="F36" s="19" t="n"/>
+      <c r="G36" s="16" t="n"/>
+      <c r="H36" s="17" t="n"/>
+      <c r="I36" s="20" t="n"/>
+      <c r="J36" s="21">
+        <f>IF(NOT(ISNUMBER($I36)),"",IF($I36&lt;TODAY(),"CADUCADO",IF($I36-TODAY()&lt;60,"RENOVAR","VIGENTE")))</f>
+      </c>
+      <c r="K36" s="22" t="n"/>
+    </row>
+    <row r="37" ht="20" customHeight="1">
+      <c r="A37" s="16" t="n"/>
+      <c r="B37" s="17" t="n"/>
+      <c r="C37" s="16" t="n"/>
+      <c r="D37" s="18" t="n"/>
+      <c r="E37" s="18" t="n"/>
+      <c r="F37" s="19" t="n"/>
+      <c r="G37" s="16" t="n"/>
+      <c r="H37" s="17" t="n"/>
+      <c r="I37" s="20" t="n"/>
+      <c r="J37" s="21">
+        <f>IF(NOT(ISNUMBER($I37)),"",IF($I37&lt;TODAY(),"CADUCADO",IF($I37-TODAY()&lt;60,"RENOVAR","VIGENTE")))</f>
+      </c>
+      <c r="K37" s="22" t="n"/>
+    </row>
+    <row r="38" ht="20" customHeight="1">
+      <c r="A38" s="16" t="n"/>
+      <c r="B38" s="17" t="n"/>
+      <c r="C38" s="16" t="n"/>
+      <c r="D38" s="18" t="n"/>
+      <c r="E38" s="18" t="n"/>
+      <c r="F38" s="19" t="n"/>
+      <c r="G38" s="16" t="n"/>
+      <c r="H38" s="17" t="n"/>
+      <c r="I38" s="20" t="n"/>
+      <c r="J38" s="21">
+        <f>IF(NOT(ISNUMBER($I38)),"",IF($I38&lt;TODAY(),"CADUCADO",IF($I38-TODAY()&lt;60,"RENOVAR","VIGENTE")))</f>
+      </c>
+      <c r="K38" s="22" t="n"/>
+    </row>
+    <row r="39" ht="20" customHeight="1">
+      <c r="A39" s="16" t="n"/>
+      <c r="B39" s="17" t="n"/>
+      <c r="C39" s="16" t="n"/>
+      <c r="D39" s="18" t="n"/>
+      <c r="E39" s="18" t="n"/>
+      <c r="F39" s="19" t="n"/>
+      <c r="G39" s="16" t="n"/>
+      <c r="H39" s="17" t="n"/>
+      <c r="I39" s="20" t="n"/>
+      <c r="J39" s="21">
+        <f>IF(NOT(ISNUMBER($I39)),"",IF($I39&lt;TODAY(),"CADUCADO",IF($I39-TODAY()&lt;60,"RENOVAR","VIGENTE")))</f>
+      </c>
+      <c r="K39" s="22" t="n"/>
+    </row>
+    <row r="40" ht="20" customHeight="1">
+      <c r="A40" s="16" t="n"/>
+      <c r="B40" s="17" t="n"/>
+      <c r="C40" s="16" t="n"/>
+      <c r="D40" s="18" t="n"/>
+      <c r="E40" s="18" t="n"/>
+      <c r="F40" s="19" t="n"/>
+      <c r="G40" s="16" t="n"/>
+      <c r="H40" s="17" t="n"/>
+      <c r="I40" s="20" t="n"/>
+      <c r="J40" s="21">
+        <f>IF(NOT(ISNUMBER($I40)),"",IF($I40&lt;TODAY(),"CADUCADO",IF($I40-TODAY()&lt;60,"RENOVAR","VIGENTE")))</f>
+      </c>
+      <c r="K40" s="22" t="n"/>
+    </row>
+    <row r="41" ht="20" customHeight="1">
+      <c r="A41" s="16" t="n"/>
+      <c r="B41" s="17" t="n"/>
+      <c r="C41" s="16" t="n"/>
+      <c r="D41" s="18" t="n"/>
+      <c r="E41" s="18" t="n"/>
+      <c r="F41" s="19" t="n"/>
+      <c r="G41" s="16" t="n"/>
+      <c r="H41" s="17" t="n"/>
+      <c r="I41" s="20" t="n"/>
+      <c r="J41" s="21">
+        <f>IF(NOT(ISNUMBER($I41)),"",IF($I41&lt;TODAY(),"CADUCADO",IF($I41-TODAY()&lt;60,"RENOVAR","VIGENTE")))</f>
+      </c>
+      <c r="K41" s="22" t="n"/>
+    </row>
+    <row r="42" ht="20" customHeight="1">
+      <c r="A42" s="16" t="n"/>
+      <c r="B42" s="17" t="n"/>
+      <c r="C42" s="16" t="n"/>
+      <c r="D42" s="18" t="n"/>
+      <c r="E42" s="18" t="n"/>
+      <c r="F42" s="19" t="n"/>
+      <c r="G42" s="16" t="n"/>
+      <c r="H42" s="17" t="n"/>
+      <c r="I42" s="20" t="n"/>
+      <c r="J42" s="21">
+        <f>IF(NOT(ISNUMBER($I42)),"",IF($I42&lt;TODAY(),"CADUCADO",IF($I42-TODAY()&lt;60,"RENOVAR","VIGENTE")))</f>
+      </c>
+      <c r="K42" s="22" t="n"/>
+    </row>
+    <row r="43" ht="20" customHeight="1">
+      <c r="A43" s="16" t="n"/>
+      <c r="B43" s="17" t="n"/>
+      <c r="C43" s="16" t="n"/>
+      <c r="D43" s="18" t="n"/>
+      <c r="E43" s="18" t="n"/>
+      <c r="F43" s="19" t="n"/>
+      <c r="G43" s="16" t="n"/>
+      <c r="H43" s="17" t="n"/>
+      <c r="I43" s="20" t="n"/>
+      <c r="J43" s="21">
+        <f>IF(NOT(ISNUMBER($I43)),"",IF($I43&lt;TODAY(),"CADUCADO",IF($I43-TODAY()&lt;60,"RENOVAR","VIGENTE")))</f>
+      </c>
+      <c r="K43" s="22" t="n"/>
+    </row>
+    <row r="44" ht="20" customHeight="1">
+      <c r="A44" s="16" t="n"/>
+      <c r="B44" s="17" t="n"/>
+      <c r="C44" s="16" t="n"/>
+      <c r="D44" s="18" t="n"/>
+      <c r="E44" s="18" t="n"/>
+      <c r="F44" s="19" t="n"/>
+      <c r="G44" s="16" t="n"/>
+      <c r="H44" s="17" t="n"/>
+      <c r="I44" s="20" t="n"/>
+      <c r="J44" s="21">
+        <f>IF(NOT(ISNUMBER($I44)),"",IF($I44&lt;TODAY(),"CADUCADO",IF($I44-TODAY()&lt;60,"RENOVAR","VIGENTE")))</f>
+      </c>
+      <c r="K44" s="22" t="n"/>
+    </row>
+    <row r="45"/>
+    <row r="46">
+      <c r="A46" s="23" t="inlineStr">
+        <is>
+          <t>Formaciones CADUCADAS:</t>
+        </is>
+      </c>
+      <c r="B46" s="24">
+        <f>COUNTIF($J$5:$J$44,"CADUCADO")</f>
+        <v>1.0</v>
+      </c>
+      <c r="C46" s="23" t="inlineStr">
+        <is>
+          <t>Caducan en menos de 60 días:</t>
+        </is>
+      </c>
+      <c r="D46" s="24">
+        <f>COUNTIF($J$5:$J$44,"RENOVAR")</f>
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="47"/>
+    <row r="48" ht="12.2" customHeight="1">
+      <c r="A48" s="25" t="inlineStr">
+        <is>
+          <t>Escribe «Válido hasta» como FECHA. La columna «Estado» la compara con el día de hoy y responde VIGENTE, RENOVAR (quedan menos de 60 días) o CADUCADO, con semáforo. Las dos casillas de arriba cuentan cuántas hay de cada.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="24.5" customHeight="1">
+      <c r="A49" s="25" t="inlineStr">
+        <is>
+          <t>El carné oficial de manipulador de alimentos se suprimió con el RD 109/2010: lo que se exige hoy es formación en higiene alimentaria acreditada POR LA EMPRESA (Reg. (CE) 852/2004, Anexo II, Cap. XII). La norma no fija una caducidad, así que la fecha de «Válido hasta» es el plazo de reciclaje que fija tu propio plan de formación; lo habitual es entre 2 y 4 años.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="12.2" customHeight="1">
+      <c r="A50" s="25" t="inlineStr">
+        <is>
+          <t>La firma del empleado es lo que acredita que recibió la formación, no sólo que la empresa la contrató. Sin ella, el registro vale la mitad.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="24.5" customHeight="1">
+      <c r="A51" s="25" t="inlineStr">
+        <is>
+          <t>Las tres primeras filas son EJEMPLOS —lo dice el nombre— y enseñan a propósito los tres estados: VIGENTE, RENOVAR y CADUCADO. Su «Válido hasta» es una fórmula relativa al día de hoy, así que el ejemplo no caduca con el tiempo; al escribir tu fecha real la fórmula desaparece y la celda pasa a ser un dato normal.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="12.2" customHeight="1">
+      <c r="A52" s="25" t="inlineStr">
+        <is>
+          <t>Conservar al menos 2 años (trazabilidad y proveedores: 5); el Reg. (CE) 178/2002 exige trazabilidad pero no fija plazo — consulta la guía de prácticas correctas de higiene de tu comunidad autónoma.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="12.2" customHeight="1">
+      <c r="A53" s="25" t="inlineStr">
         <is>
           <t>— Pack de Plantillas APPCC · AI Chef Pro · aichef.pro</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:H1"/>
+  <mergeCells count="7">
+    <mergeCell ref="A52:K52"/>
+    <mergeCell ref="A49:K49"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A51:K51"/>
+    <mergeCell ref="A53:K53"/>
+    <mergeCell ref="A50:K50"/>
+    <mergeCell ref="A48:K48"/>
   </mergeCells>
-  <dataValidations count="1">
-    <dataValidation sqref="C4 C5 C6 C7 C8 C9 C10 C11 C12 C13 C14 C15 C16 C17 C18 C19 C20 C21 C22 C23" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"Manipulador alimentos,APPCC básico,APPCC avanzado,Alérgenos,Primeros auxilios,Prevención riesgos,Atención al cliente,Otro"</formula1>
+  <conditionalFormatting sqref="J5:J44">
+    <cfRule type="expression" priority="1" dxfId="0" stopIfTrue="1">
+      <formula>OR(J5="ALERTA",J5="RECHAZAR",J5="CAMBIAR",J5="REVISAR",J5="✗",J5="CADUCADO",J5="EXCESO")</formula>
+    </cfRule>
+    <cfRule type="expression" priority="2" dxfId="1" stopIfTrue="1">
+      <formula>OR(J5="VIGILAR",J5="⚠",J5="INCOMPLETO",J5="CADUCA PRONTO",J5="RENOVAR",J5="FALTA CLORO",J5="FALTA TEST")</formula>
+    </cfRule>
+    <cfRule type="expression" priority="3" dxfId="2" stopIfTrue="1">
+      <formula>OR(J5="OK",J5="✓",J5="Cumple",J5="VIGENTE",J5="Completo",J5="APTO")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B46">
+    <cfRule type="expression" priority="4" dxfId="0" stopIfTrue="1">
+      <formula>B46&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D46">
+    <cfRule type="expression" priority="5" dxfId="1" stopIfTrue="1">
+      <formula>D46&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="5">
+    <dataValidation sqref="C5:C44" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Formación recibida" error="Elige una formación de la lista o «Otra» y detállala en el nombre del certificado." type="list" errorStyle="stop">
+      <formula1>"Higiene alimentaria (manipulación de alimentos),APPCC básico,APPCC avanzado,Alérgenos e información al consumidor,Limpieza y desinfección,Primeros auxilios,Prevención de riesgos laborales,Otra"</formula1>
+    </dataValidation>
+    <dataValidation sqref="D5:D44" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Fecha" error="Escribe una fecha (por ejemplo 15/03/2026). Si la celda se queda como texto, la columna «Estado» no puede compararla con el día de hoy y se queda en blanco." type="date" errorStyle="stop" operator="between">
+      <formula1>DATE(2000,1,1)</formula1>
+      <formula2>DATE(2100,12,31)</formula2>
+    </dataValidation>
+    <dataValidation sqref="E5:E44" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Fecha" error="Escribe una fecha (por ejemplo 15/03/2026). Si la celda se queda como texto, la columna «Estado» no puede compararla con el día de hoy y se queda en blanco." type="date" errorStyle="stop" operator="between">
+      <formula1>DATE(2000,1,1)</formula1>
+      <formula2>DATE(2100,12,31)</formula2>
+    </dataValidation>
+    <dataValidation sqref="I5:I44" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Fecha" error="Escribe una fecha (por ejemplo 15/03/2026). Si la celda se queda como texto, la columna «Estado» no puede compararla con el día de hoy y se queda en blanco." type="date" errorStyle="stop" operator="between">
+      <formula1>DATE(2000,1,1)</formula1>
+      <formula2>DATE(2100,12,31)</formula2>
+    </dataValidation>
+    <dataValidation sqref="F5:F44" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Duración" error="Introduce la duración en horas, entre 0 y 500." type="decimal" errorStyle="stop" operator="between">
+      <formula1>0</formula1>
+      <formula2>500</formula2>
     </dataValidation>
   </dataValidations>
-  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageMargins left="0.55" right="0.55" top="0.55" bottom="0.55" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader/>

--- a/astro-site/public/dl/pack-appcc/BONUS-01-registro-formacion.xlsx
+++ b/astro-site/public/dl/pack-appcc/BONUS-01-registro-formacion.xlsx
@@ -918,10 +918,10 @@
         </is>
       </c>
       <c r="D5" s="18" t="n">
-        <v>46061</v>
+        <v>46068</v>
       </c>
       <c r="E5" s="18" t="n">
-        <v>46061</v>
+        <v>46068</v>
       </c>
       <c r="F5" s="19" t="n">
         <v>6</v>
@@ -933,12 +933,12 @@
       </c>
       <c r="H5" s="17" t="inlineStr">
         <is>
-          <t>CERT-2026-0039</t>
+          <t>CERT-2026-0046</t>
         </is>
       </c>
       <c r="I5" s="20">
         <f>TODAY()+900</f>
-        <v>47156.0</v>
+        <v>47163.0</v>
       </c>
       <c r="J5" s="21" t="str">
         <f>IF(NOT(ISNUMBER($I5)),"",IF($I5&lt;TODAY(),"CADUCADO",IF($I5-TODAY()&lt;60,"RENOVAR","VIGENTE")))</f>
@@ -967,10 +967,10 @@
         </is>
       </c>
       <c r="D6" s="18" t="n">
-        <v>45191</v>
+        <v>45198</v>
       </c>
       <c r="E6" s="18" t="n">
-        <v>45191</v>
+        <v>45198</v>
       </c>
       <c r="F6" s="19" t="n">
         <v>4</v>
@@ -982,12 +982,12 @@
       </c>
       <c r="H6" s="17" t="inlineStr">
         <is>
-          <t>CERT-2023-0265</t>
+          <t>CERT-2023-0272</t>
         </is>
       </c>
       <c r="I6" s="20">
         <f>TODAY()+30</f>
-        <v>46286.0</v>
+        <v>46293.0</v>
       </c>
       <c r="J6" s="21" t="str">
         <f>IF(NOT(ISNUMBER($I6)),"",IF($I6&lt;TODAY(),"CADUCADO",IF($I6-TODAY()&lt;60,"RENOVAR","VIGENTE")))</f>
@@ -1016,10 +1016,10 @@
         </is>
       </c>
       <c r="D7" s="18" t="n">
-        <v>45101</v>
+        <v>45108</v>
       </c>
       <c r="E7" s="18" t="n">
-        <v>45101</v>
+        <v>45108</v>
       </c>
       <c r="F7" s="19" t="n">
         <v>6</v>
@@ -1031,12 +1031,12 @@
       </c>
       <c r="H7" s="17" t="inlineStr">
         <is>
-          <t>CERT-2023-0175</t>
+          <t>CERT-2023-0182</t>
         </is>
       </c>
       <c r="I7" s="20">
         <f>TODAY()-60</f>
-        <v>46196.0</v>
+        <v>46203.0</v>
       </c>
       <c r="J7" s="21" t="str">
         <f>IF(NOT(ISNUMBER($I7)),"",IF($I7&lt;TODAY(),"CADUCADO",IF($I7-TODAY()&lt;60,"RENOVAR","VIGENTE")))</f>
@@ -1672,8 +1672,8 @@
     <mergeCell ref="A52:K52"/>
     <mergeCell ref="A49:K49"/>
     <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A53:K53"/>
     <mergeCell ref="A51:K51"/>
-    <mergeCell ref="A53:K53"/>
     <mergeCell ref="A50:K50"/>
     <mergeCell ref="A48:K48"/>
   </mergeCells>
